--- a/artfynd/A 14667-2020 artfynd.xlsx
+++ b/artfynd/A 14667-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14667-2020 artfynd.xlsx
+++ b/artfynd/A 14667-2020 artfynd.xlsx
@@ -1062,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117686885</v>
+        <v>117688332</v>
       </c>
       <c r="B5" t="n">
-        <v>57930</v>
+        <v>57438</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,20 +1074,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117688332</v>
+        <v>117686885</v>
       </c>
       <c r="B6" t="n">
-        <v>57438</v>
+        <v>57930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1282,22 +1282,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14667-2020 artfynd.xlsx
+++ b/artfynd/A 14667-2020 artfynd.xlsx
@@ -1062,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117688332</v>
+        <v>117686885</v>
       </c>
       <c r="B5" t="n">
-        <v>57438</v>
+        <v>57931</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1074,20 +1074,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>06:37</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117686885</v>
+        <v>117686863</v>
       </c>
       <c r="B6" t="n">
-        <v>57930</v>
+        <v>57657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117686863</v>
+        <v>117688332</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57439</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1415,22 +1415,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>06:37</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 14667-2020 artfynd.xlsx
+++ b/artfynd/A 14667-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1459,6 +1459,390 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126203503</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lysninge, 640 m nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>639479</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6520779</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Ohlsberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Ohlsberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Punkttaxering Nynäs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126205085</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lysninge, 640 m nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>639479</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6520779</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Ohlsberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Ohlsberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Punkttaxering Nynäs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126203524</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lysninge, 640 m nordväst, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>639479</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6520779</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>S20</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Ohlsberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Ohlsberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Punkttaxering Nynäs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14667-2020 artfynd.xlsx
+++ b/artfynd/A 14667-2020 artfynd.xlsx
@@ -1464,7 +1464,7 @@
         <v>126203503</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>126205085</v>
       </c>
       <c r="B9" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126203524</v>
       </c>
       <c r="B10" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14667-2020 artfynd.xlsx
+++ b/artfynd/A 14667-2020 artfynd.xlsx
@@ -1464,7 +1464,7 @@
         <v>126203503</v>
       </c>
       <c r="B8" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>126205085</v>
       </c>
       <c r="B9" t="n">
-        <v>58135</v>
+        <v>58138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126203524</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
